--- a/artfynd/A 1824-2026 artfynd.xlsx
+++ b/artfynd/A 1824-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>123232877</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -802,19 +797,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123235138</v>
+        <v>123235031</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441506</v>
+        <v>441542</v>
       </c>
       <c r="R3" t="n">
-        <v>7028655</v>
+        <v>7028672</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -882,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gammal gran.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,6 +921,248 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123235138</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>441506</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7028655</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gammal gran.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>93503048</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Raskhus V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>441280</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7028442</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-05-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-05-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Liten stam i kanten av kärrvägen.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1824-2026 artfynd.xlsx
+++ b/artfynd/A 1824-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123232877</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,6 +931,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123235031</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,6 +1063,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123235138</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1163,8 +1183,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93503048</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>